--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_4/epoch_140/per_file_predictions_epoch_140.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_4/epoch_140/per_file_predictions_epoch_140.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="518">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,766 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9203,0.0136,0.0068,0.0277</t>
-  </si>
-  <si>
-    <t>0.8817,0.0183,0.0050,0.0305</t>
-  </si>
-  <si>
-    <t>0.6848,0.0241,0.0060,0.1649</t>
-  </si>
-  <si>
-    <t>0.8041,0.0191,0.0020,0.0415</t>
-  </si>
-  <si>
-    <t>0.7739,0.0638,0.0056,0.0270</t>
-  </si>
-  <si>
-    <t>0.8081,0.1049,0.0093,0.0115</t>
-  </si>
-  <si>
-    <t>0.8036,0.0763,0.0132,0.0211</t>
-  </si>
-  <si>
-    <t>0.8519,0.0582,0.0028,0.0088</t>
-  </si>
-  <si>
-    <t>0.7801,0.0722,0.0115,0.0277</t>
-  </si>
-  <si>
-    <t>0.7093,0.1133,0.0135,0.0310</t>
-  </si>
-  <si>
-    <t>0.6927,0.0844,0.0026,0.0148</t>
-  </si>
-  <si>
-    <t>0.7482,0.1539,0.0098,0.0103</t>
-  </si>
-  <si>
-    <t>0.9254,0.0168,0.0055,0.0130</t>
-  </si>
-  <si>
-    <t>0.9036,0.0318,0.0099,0.0140</t>
-  </si>
-  <si>
-    <t>0.8241,0.0590,0.0740,0.0204</t>
-  </si>
-  <si>
-    <t>0.7677,0.0276,0.1830,0.0390</t>
-  </si>
-  <si>
-    <t>0.8821,0.0382,0.0217,0.0115</t>
-  </si>
-  <si>
-    <t>0.6241,0.2698,0.0191,0.0092</t>
-  </si>
-  <si>
-    <t>0.3863,0.4971,0.0172,0.0116</t>
-  </si>
-  <si>
-    <t>0.6111,0.2143,0.0051,0.0105</t>
-  </si>
-  <si>
-    <t>0.2272,0.5999,0.0550,0.0284</t>
-  </si>
-  <si>
-    <t>0.0084,0.9798,0.0191,0.0056</t>
-  </si>
-  <si>
-    <t>0.9523,0.0070,0.0127,0.0067</t>
-  </si>
-  <si>
-    <t>0.7982,0.0410,0.0966,0.0259</t>
-  </si>
-  <si>
-    <t>0.8685,0.0037,0.1369,0.0047</t>
-  </si>
-  <si>
-    <t>0.7275,0.1061,0.1503,0.0324</t>
-  </si>
-  <si>
-    <t>0.6888,0.0648,0.1828,0.0665</t>
-  </si>
-  <si>
-    <t>0.9092,0.0086,0.0216,0.0230</t>
-  </si>
-  <si>
-    <t>0.7430,0.0056,0.3047,0.0059</t>
-  </si>
-  <si>
-    <t>0.7581,0.1542,0.0042,0.0062</t>
-  </si>
-  <si>
-    <t>0.7478,0.0833,0.0184,0.0422</t>
-  </si>
-  <si>
-    <t>0.0110,0.4135,0.9787,0.0009</t>
-  </si>
-  <si>
-    <t>0.7251,0.1711,0.0085,0.0123</t>
-  </si>
-  <si>
-    <t>0.7576,0.0167,0.0040,0.1221</t>
-  </si>
-  <si>
-    <t>0.5625,0.2468,0.1116,0.0579</t>
-  </si>
-  <si>
-    <t>0.7882,0.0924,0.0062,0.0142</t>
-  </si>
-  <si>
-    <t>0.4148,0.3179,0.0865,0.0662</t>
-  </si>
-  <si>
-    <t>0.7117,0.1118,0.1440,0.0498</t>
-  </si>
-  <si>
-    <t>0.9169,0.0053,0.0829,0.0051</t>
-  </si>
-  <si>
-    <t>0.8301,0.0026,0.2309,0.0028</t>
-  </si>
-  <si>
-    <t>0.7973,0.0498,0.1081,0.0240</t>
-  </si>
-  <si>
-    <t>0.4194,0.0427,0.5548,0.0226</t>
-  </si>
-  <si>
-    <t>0.6525,0.3315,0.0341,0.0093</t>
-  </si>
-  <si>
-    <t>0.8381,0.0215,0.1128,0.0184</t>
-  </si>
-  <si>
-    <t>0.8304,0.0222,0.0085,0.0548</t>
-  </si>
-  <si>
-    <t>0.6518,0.1378,0.0040,0.0208</t>
-  </si>
-  <si>
-    <t>0.3020,0.5580,0.0185,0.0129</t>
-  </si>
-  <si>
-    <t>0.2941,0.6308,0.0407,0.0134</t>
-  </si>
-  <si>
-    <t>0.0521,0.1029,0.9297,0.0022</t>
-  </si>
-  <si>
-    <t>0.2059,0.0248,0.8610,0.0019</t>
-  </si>
-  <si>
-    <t>0.6527,0.0139,0.4676,0.0028</t>
-  </si>
-  <si>
-    <t>0.6093,0.0369,0.4364,0.0044</t>
-  </si>
-  <si>
-    <t>0.1374,0.3505,0.8229,0.0069</t>
-  </si>
-  <si>
-    <t>0.6974,0.0356,0.3461,0.0093</t>
-  </si>
-  <si>
-    <t>0.8126,0.0423,0.0035,0.0247</t>
-  </si>
-  <si>
-    <t>0.7488,0.0731,0.0106,0.0383</t>
-  </si>
-  <si>
-    <t>0.7558,0.0775,0.0142,0.0476</t>
-  </si>
-  <si>
-    <t>0.1338,0.6749,0.4859,0.0386</t>
-  </si>
-  <si>
-    <t>0.8284,0.0558,0.0065,0.0155</t>
-  </si>
-  <si>
-    <t>0.8099,0.0372,0.0050,0.0359</t>
-  </si>
-  <si>
-    <t>0.7811,0.1131,0.0155,0.0183</t>
-  </si>
-  <si>
-    <t>0.0764,0.7721,0.5796,0.0046</t>
-  </si>
-  <si>
-    <t>0.2428,0.2133,0.7073,0.0087</t>
-  </si>
-  <si>
-    <t>0.8204,0.0082,0.1792,0.0071</t>
-  </si>
-  <si>
-    <t>0.0629,0.7228,0.7007,0.0013</t>
-  </si>
-  <si>
-    <t>0.2416,0.0343,0.8287,0.0052</t>
-  </si>
-  <si>
-    <t>0.3205,0.6107,0.0179,0.0080</t>
-  </si>
-  <si>
-    <t>0.0043,0.9958,0.0053,0.0001</t>
-  </si>
-  <si>
-    <t>0.8952,0.0230,0.0088,0.0214</t>
-  </si>
-  <si>
-    <t>0.8204,0.0283,0.0028,0.0310</t>
-  </si>
-  <si>
-    <t>0.0180,0.4317,0.9478,0.0015</t>
-  </si>
-  <si>
-    <t>0.2536,0.5249,0.3885,0.0059</t>
-  </si>
-  <si>
-    <t>0.6733,0.1128,0.1997,0.0156</t>
-  </si>
-  <si>
-    <t>0.0123,0.9353,0.6747,0.0027</t>
-  </si>
-  <si>
-    <t>0.0075,0.9748,0.4722,0.0011</t>
-  </si>
-  <si>
-    <t>0.6739,0.0433,0.0383,0.1662</t>
-  </si>
-  <si>
-    <t>0.8581,0.0154,0.0065,0.0589</t>
-  </si>
-  <si>
-    <t>0.8467,0.0241,0.0073,0.0548</t>
-  </si>
-  <si>
-    <t>0.5712,0.0507,0.0230,0.2646</t>
-  </si>
-  <si>
-    <t>0.7955,0.0473,0.0375,0.0695</t>
-  </si>
-  <si>
-    <t>0.6991,0.0482,0.0366,0.1830</t>
-  </si>
-  <si>
-    <t>0.2279,0.1880,0.7100,0.0085</t>
-  </si>
-  <si>
-    <t>0.1897,0.3414,0.6837,0.0231</t>
-  </si>
-  <si>
-    <t>0.6750,0.0956,0.2102,0.0251</t>
-  </si>
-  <si>
-    <t>0.1928,0.2890,0.6667,0.0141</t>
-  </si>
-  <si>
-    <t>0.2365,0.4664,0.4636,0.0041</t>
-  </si>
-  <si>
-    <t>0.4716,0.1849,0.4174,0.0048</t>
-  </si>
-  <si>
-    <t>0.6441,0.0962,0.0196,0.0783</t>
-  </si>
-  <si>
-    <t>0.7409,0.1120,0.0112,0.0176</t>
-  </si>
-  <si>
-    <t>0.8157,0.0431,0.0140,0.0489</t>
-  </si>
-  <si>
-    <t>0.7367,0.0585,0.0066,0.0337</t>
-  </si>
-  <si>
-    <t>0.8736,0.0285,0.0038,0.0185</t>
-  </si>
-  <si>
-    <t>0.6362,0.1162,0.0153,0.0400</t>
-  </si>
-  <si>
-    <t>0.8101,0.0123,0.0020,0.0628</t>
-  </si>
-  <si>
-    <t>0.7923,0.0952,0.0168,0.0243</t>
-  </si>
-  <si>
-    <t>0.7346,0.0514,0.0107,0.0534</t>
-  </si>
-  <si>
-    <t>0.8085,0.1184,0.0041,0.0052</t>
-  </si>
-  <si>
-    <t>0.8039,0.0371,0.0038,0.0353</t>
-  </si>
-  <si>
-    <t>0.8826,0.0451,0.0084,0.0184</t>
-  </si>
-  <si>
-    <t>0.9229,0.0287,0.0033,0.0098</t>
-  </si>
-  <si>
-    <t>0.8304,0.0548,0.0144,0.0321</t>
-  </si>
-  <si>
-    <t>0.9005,0.0642,0.0039,0.0045</t>
-  </si>
-  <si>
-    <t>0.6794,0.0523,0.0134,0.1043</t>
-  </si>
-  <si>
-    <t>0.1621,0.0758,0.8540,0.0279</t>
-  </si>
-  <si>
-    <t>0.5180,0.0774,0.4513,0.0257</t>
-  </si>
-  <si>
-    <t>0.9373,0.0080,0.0134,0.0107</t>
-  </si>
-  <si>
-    <t>0.9168,0.0082,0.0694,0.0030</t>
-  </si>
-  <si>
-    <t>0.4944,0.3468,0.0338,0.0272</t>
-  </si>
-  <si>
-    <t>0.2007,0.7443,0.0292,0.0112</t>
-  </si>
-  <si>
-    <t>0.0308,0.9256,0.0323,0.0154</t>
-  </si>
-  <si>
-    <t>0.3824,0.5127,0.0084,0.0059</t>
-  </si>
-  <si>
-    <t>0.6971,0.1389,0.0119,0.0198</t>
-  </si>
-  <si>
-    <t>0.3680,0.3873,0.0039,0.0136</t>
-  </si>
-  <si>
-    <t>0.7120,0.1717,0.0068,0.0089</t>
-  </si>
-  <si>
-    <t>0.9141,0.0170,0.0131,0.0238</t>
-  </si>
-  <si>
-    <t>0.9469,0.0048,0.0056,0.0163</t>
-  </si>
-  <si>
-    <t>0.9219,0.0176,0.0370,0.0080</t>
-  </si>
-  <si>
-    <t>0.8975,0.0689,0.0077,0.0042</t>
-  </si>
-  <si>
-    <t>0.7033,0.0916,0.0455,0.0715</t>
-  </si>
-  <si>
-    <t>0.1882,0.7913,0.0367,0.0056</t>
-  </si>
-  <si>
-    <t>0.5812,0.2567,0.0576,0.0320</t>
-  </si>
-  <si>
-    <t>0.8235,0.0358,0.0124,0.0397</t>
-  </si>
-  <si>
-    <t>0.0221,0.9290,0.6525,0.0066</t>
-  </si>
-  <si>
-    <t>0.9143,0.0271,0.0022,0.0075</t>
-  </si>
-  <si>
-    <t>0.6043,0.1133,0.0181,0.0617</t>
-  </si>
-  <si>
-    <t>0.6806,0.1121,0.0243,0.0629</t>
-  </si>
-  <si>
-    <t>0.8369,0.0703,0.0104,0.0184</t>
-  </si>
-  <si>
-    <t>0.8042,0.0809,0.0170,0.0271</t>
-  </si>
-  <si>
-    <t>0.8271,0.0533,0.0065,0.0243</t>
-  </si>
-  <si>
-    <t>0.7099,0.1366,0.0146,0.0232</t>
-  </si>
-  <si>
-    <t>0.9021,0.0424,0.0135,0.0126</t>
-  </si>
-  <si>
-    <t>0.8138,0.0843,0.0141,0.0180</t>
-  </si>
-  <si>
-    <t>0.5894,0.1026,0.0243,0.1023</t>
-  </si>
-  <si>
-    <t>0.8848,0.0349,0.0057,0.0180</t>
-  </si>
-  <si>
-    <t>0.5709,0.0792,0.3937,0.0090</t>
-  </si>
-  <si>
-    <t>0.7466,0.1016,0.1555,0.0118</t>
-  </si>
-  <si>
-    <t>0.4292,0.1337,0.4941,0.0224</t>
-  </si>
-  <si>
-    <t>0.5470,0.0109,0.5328,0.0075</t>
-  </si>
-  <si>
-    <t>0.5909,0.1783,0.0433,0.0615</t>
-  </si>
-  <si>
-    <t>0.5396,0.3319,0.0840,0.0164</t>
-  </si>
-  <si>
-    <t>0.9462,0.0073,0.0113,0.0111</t>
-  </si>
-  <si>
-    <t>0.7090,0.1682,0.0196,0.0181</t>
-  </si>
-  <si>
-    <t>0.8178,0.0108,0.0062,0.1224</t>
-  </si>
-  <si>
-    <t>0.7433,0.0111,0.0055,0.2115</t>
-  </si>
-  <si>
-    <t>0.9492,0.0131,0.0023,0.0093</t>
-  </si>
-  <si>
-    <t>0.9074,0.0089,0.0105,0.0539</t>
-  </si>
-  <si>
-    <t>0.0280,0.8971,0.5919,0.0141</t>
-  </si>
-  <si>
-    <t>0.8393,0.0871,0.0098,0.0078</t>
-  </si>
-  <si>
-    <t>0.3358,0.5069,0.0291,0.0213</t>
-  </si>
-  <si>
-    <t>0.8528,0.1121,0.0069,0.0048</t>
-  </si>
-  <si>
-    <t>0.5831,0.3012,0.0235,0.0088</t>
-  </si>
-  <si>
-    <t>0.9179,0.0154,0.0037,0.0184</t>
-  </si>
-  <si>
-    <t>0.8548,0.0148,0.0026,0.0530</t>
-  </si>
-  <si>
-    <t>0.8829,0.0510,0.0117,0.0152</t>
-  </si>
-  <si>
-    <t>0.0497,0.7633,0.6240,0.0471</t>
-  </si>
-  <si>
-    <t>0.9272,0.0120,0.0071,0.0192</t>
-  </si>
-  <si>
-    <t>0.9339,0.0210,0.0022,0.0060</t>
-  </si>
-  <si>
-    <t>0.5563,0.3597,0.0321,0.0164</t>
-  </si>
-  <si>
-    <t>0.8572,0.0218,0.0079,0.0478</t>
-  </si>
-  <si>
-    <t>0.8068,0.0811,0.0225,0.0173</t>
-  </si>
-  <si>
-    <t>0.7388,0.0758,0.0187,0.0574</t>
-  </si>
-  <si>
-    <t>0.8157,0.0859,0.0120,0.0163</t>
-  </si>
-  <si>
-    <t>0.9138,0.0319,0.0040,0.0069</t>
-  </si>
-  <si>
-    <t>0.7808,0.1655,0.0047,0.0044</t>
-  </si>
-  <si>
-    <t>0.6715,0.0176,0.0044,0.2193</t>
-  </si>
-  <si>
-    <t>0.7085,0.1001,0.0158,0.0362</t>
-  </si>
-  <si>
-    <t>0.8459,0.0407,0.0111,0.0361</t>
-  </si>
-  <si>
-    <t>0.7694,0.0836,0.0150,0.0353</t>
-  </si>
-  <si>
-    <t>0.8986,0.0278,0.0036,0.0133</t>
-  </si>
-  <si>
-    <t>0.7216,0.1175,0.0182,0.0276</t>
-  </si>
-  <si>
-    <t>0.6376,0.0940,0.0186,0.0830</t>
-  </si>
-  <si>
-    <t>0.6660,0.1530,0.0055,0.0119</t>
-  </si>
-  <si>
-    <t>0.3908,0.4932,0.0092,0.0076</t>
-  </si>
-  <si>
-    <t>0.5855,0.3612,0.0152,0.0097</t>
-  </si>
-  <si>
-    <t>0.5123,0.1624,0.0233,0.0791</t>
-  </si>
-  <si>
-    <t>0.4403,0.5857,0.0558,0.0060</t>
-  </si>
-  <si>
-    <t>0.4319,0.3095,0.0691,0.0622</t>
-  </si>
-  <si>
-    <t>0.7493,0.0843,0.0062,0.0221</t>
-  </si>
-  <si>
-    <t>0.7291,0.0367,0.0063,0.0762</t>
-  </si>
-  <si>
-    <t>0.0036,0.7006,0.9813,0.0008</t>
-  </si>
-  <si>
-    <t>0.7917,0.0637,0.0232,0.0491</t>
-  </si>
-  <si>
-    <t>0.2866,0.1743,0.6513,0.0169</t>
-  </si>
-  <si>
-    <t>0.2988,0.1050,0.6707,0.0150</t>
-  </si>
-  <si>
-    <t>0.5659,0.0918,0.2929,0.0559</t>
-  </si>
-  <si>
-    <t>0.2889,0.1018,0.7178,0.0130</t>
-  </si>
-  <si>
-    <t>0.5144,0.0368,0.5675,0.0094</t>
-  </si>
-  <si>
-    <t>0.9144,0.0177,0.0512,0.0040</t>
-  </si>
-  <si>
-    <t>0.5323,0.0322,0.5500,0.0079</t>
-  </si>
-  <si>
-    <t>0.9367,0.0181,0.0157,0.0064</t>
-  </si>
-  <si>
-    <t>0.9303,0.0084,0.0215,0.0148</t>
-  </si>
-  <si>
-    <t>0.7018,0.0697,0.0649,0.0921</t>
-  </si>
-  <si>
-    <t>0.8800,0.0198,0.0313,0.0292</t>
-  </si>
-  <si>
-    <t>0.8952,0.0215,0.0212,0.0294</t>
-  </si>
-  <si>
-    <t>0.9234,0.0121,0.0379,0.0110</t>
-  </si>
-  <si>
-    <t>0.9273,0.0126,0.0143,0.0284</t>
-  </si>
-  <si>
-    <t>0.8569,0.0387,0.0189,0.0245</t>
-  </si>
-  <si>
-    <t>0.7281,0.1255,0.0154,0.0217</t>
-  </si>
-  <si>
-    <t>0.5156,0.3002,0.0134,0.0129</t>
-  </si>
-  <si>
-    <t>0.5798,0.2620,0.0257,0.0243</t>
-  </si>
-  <si>
-    <t>0.8103,0.1003,0.0068,0.0082</t>
-  </si>
-  <si>
-    <t>0.7149,0.0881,0.0133,0.0385</t>
-  </si>
-  <si>
-    <t>0.8776,0.0283,0.0182,0.0291</t>
-  </si>
-  <si>
-    <t>0.9457,0.0079,0.0045,0.0135</t>
-  </si>
-  <si>
-    <t>0.9577,0.0124,0.0048,0.0051</t>
-  </si>
-  <si>
-    <t>0.9642,0.0060,0.0070,0.0053</t>
-  </si>
-  <si>
-    <t>0.9095,0.0105,0.0345,0.0191</t>
-  </si>
-  <si>
-    <t>0.2092,0.0600,0.7935,0.0135</t>
-  </si>
-  <si>
-    <t>0.3657,0.2093,0.4705,0.0508</t>
-  </si>
-  <si>
-    <t>0.9160,0.0135,0.0264,0.0159</t>
-  </si>
-  <si>
-    <t>0.8253,0.0067,0.1375,0.0192</t>
-  </si>
-  <si>
-    <t>0.6448,0.0436,0.3168,0.0091</t>
-  </si>
-  <si>
-    <t>0.7123,0.1061,0.0206,0.0422</t>
-  </si>
-  <si>
-    <t>0.7822,0.0996,0.0047,0.0095</t>
-  </si>
-  <si>
-    <t>0.7786,0.0352,0.0057,0.0551</t>
-  </si>
-  <si>
-    <t>0.7605,0.1072,0.0126,0.0219</t>
-  </si>
-  <si>
-    <t>0.8437,0.0411,0.0101,0.0254</t>
-  </si>
-  <si>
-    <t>0.8399,0.0581,0.0082,0.0175</t>
-  </si>
-  <si>
-    <t>0.6612,0.1618,0.0415,0.0478</t>
-  </si>
-  <si>
-    <t>0.7030,0.1577,0.0279,0.0290</t>
-  </si>
-  <si>
-    <t>0.8117,0.0408,0.1353,0.0383</t>
-  </si>
-  <si>
-    <t>0.7570,0.0622,0.0154,0.0573</t>
-  </si>
-  <si>
-    <t>0.8482,0.0433,0.0149,0.0281</t>
-  </si>
-  <si>
-    <t>0.2363,0.0315,0.8608,0.0010</t>
-  </si>
-  <si>
-    <t>0.6219,0.0283,0.4051,0.0249</t>
-  </si>
-  <si>
-    <t>0.5585,0.0386,0.5159,0.0103</t>
-  </si>
-  <si>
-    <t>0.1467,0.1538,0.8703,0.0062</t>
-  </si>
-  <si>
-    <t>0.9387,0.0073,0.0364,0.0046</t>
-  </si>
-  <si>
-    <t>0.1837,0.0327,0.8807,0.0029</t>
-  </si>
-  <si>
-    <t>0.4785,0.0871,0.4070,0.0534</t>
-  </si>
-  <si>
-    <t>0.6668,0.0580,0.2199,0.0684</t>
-  </si>
-  <si>
-    <t>0.9374,0.0090,0.0054,0.0125</t>
-  </si>
-  <si>
-    <t>0.9206,0.0078,0.0143,0.0243</t>
-  </si>
-  <si>
-    <t>0.9185,0.0201,0.0161,0.0183</t>
-  </si>
-  <si>
-    <t>0.8629,0.0610,0.0045,0.0098</t>
-  </si>
-  <si>
-    <t>0.7228,0.1168,0.0146,0.0237</t>
-  </si>
-  <si>
-    <t>0.6684,0.2533,0.0222,0.0144</t>
-  </si>
-  <si>
-    <t>0.5588,0.1315,0.0213,0.0840</t>
-  </si>
-  <si>
-    <t>0.7536,0.0983,0.0065,0.0186</t>
-  </si>
-  <si>
-    <t>0.7575,0.0914,0.0121,0.0269</t>
-  </si>
-  <si>
-    <t>0.4841,0.1169,0.0176,0.1286</t>
-  </si>
-  <si>
-    <t>0.7388,0.0762,0.0117,0.0448</t>
-  </si>
-  <si>
-    <t>0.8600,0.0143,0.1086,0.0140</t>
-  </si>
-  <si>
-    <t>0.2789,0.0822,0.7526,0.0078</t>
-  </si>
-  <si>
-    <t>0.1763,0.1797,0.7836,0.0187</t>
-  </si>
-  <si>
-    <t>0.8324,0.0336,0.1064,0.0120</t>
-  </si>
-  <si>
-    <t>0.4070,0.0239,0.7042,0.0022</t>
-  </si>
-  <si>
-    <t>0.8897,0.0257,0.0215,0.0233</t>
-  </si>
-  <si>
-    <t>0.9196,0.0193,0.0125,0.0102</t>
-  </si>
-  <si>
-    <t>0.5913,0.0142,0.4793,0.0132</t>
-  </si>
-  <si>
-    <t>0.9062,0.0300,0.0045,0.0085</t>
-  </si>
-  <si>
-    <t>0.7358,0.0323,0.0174,0.1328</t>
-  </si>
-  <si>
-    <t>0.9085,0.0181,0.0026,0.0196</t>
-  </si>
-  <si>
-    <t>0.5619,0.0553,0.0413,0.3314</t>
-  </si>
-  <si>
-    <t>0.8695,0.0150,0.0058,0.0520</t>
-  </si>
-  <si>
-    <t>0.8191,0.0355,0.0171,0.0477</t>
+    <t>0.9809,0.0063,0.0046,0.0019</t>
+  </si>
+  <si>
+    <t>0.0165,0.0003,0.0008,0.9942</t>
+  </si>
+  <si>
+    <t>0.7990,0.0014,0.0085,0.2270</t>
+  </si>
+  <si>
+    <t>0.6317,0.0125,0.0082,0.4344</t>
+  </si>
+  <si>
+    <t>0.9969,0.0006,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.9938,0.0010,0.0009,0.0013</t>
+  </si>
+  <si>
+    <t>0.9960,0.0006,0.0003,0.0010</t>
+  </si>
+  <si>
+    <t>0.9976,0.0003,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9948,0.0017,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9951,0.0021,0.0011,0.0003</t>
+  </si>
+  <si>
+    <t>0.9967,0.0009,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9953,0.0007,0.0001,0.0013</t>
+  </si>
+  <si>
+    <t>0.8150,0.0095,0.2701,0.0018</t>
+  </si>
+  <si>
+    <t>0.1107,0.0124,0.9135,0.0012</t>
+  </si>
+  <si>
+    <t>0.5519,0.0075,0.6584,0.0002</t>
+  </si>
+  <si>
+    <t>0.0103,0.0012,0.9872,0.0010</t>
+  </si>
+  <si>
+    <t>0.9523,0.0026,0.0486,0.0018</t>
+  </si>
+  <si>
+    <t>0.0016,0.9962,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.0017,0.9956,0.0008,0.0005</t>
+  </si>
+  <si>
+    <t>0.0442,0.9598,0.0017,0.0009</t>
+  </si>
+  <si>
+    <t>0.0117,0.9840,0.0041,0.0006</t>
+  </si>
+  <si>
+    <t>0.0003,0.9989,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.7370,0.0114,0.3565,0.0044</t>
+  </si>
+  <si>
+    <t>0.7555,0.0043,0.3010,0.0128</t>
+  </si>
+  <si>
+    <t>0.0040,0.0013,0.9950,0.0005</t>
+  </si>
+  <si>
+    <t>0.0385,0.0086,0.9485,0.0023</t>
+  </si>
+  <si>
+    <t>0.0283,0.0035,0.9795,0.0010</t>
+  </si>
+  <si>
+    <t>0.0142,0.0048,0.9771,0.0028</t>
+  </si>
+  <si>
+    <t>0.0114,0.0014,0.9819,0.0091</t>
+  </si>
+  <si>
+    <t>0.7591,0.4082,0.0012,0.0002</t>
+  </si>
+  <si>
+    <t>0.8706,0.0181,0.1375,0.0025</t>
+  </si>
+  <si>
+    <t>0.0008,0.0168,0.9946,0.0046</t>
+  </si>
+  <si>
+    <t>0.0279,0.9034,0.0809,0.0010</t>
+  </si>
+  <si>
+    <t>0.9462,0.0540,0.0017,0.0022</t>
+  </si>
+  <si>
+    <t>0.0928,0.0243,0.9038,0.0047</t>
+  </si>
+  <si>
+    <t>0.9524,0.0625,0.0032,0.0005</t>
+  </si>
+  <si>
+    <t>0.0019,0.9919,0.2193,0.0008</t>
+  </si>
+  <si>
+    <t>0.0288,0.1457,0.8845,0.0013</t>
+  </si>
+  <si>
+    <t>0.2721,0.0010,0.7527,0.0067</t>
+  </si>
+  <si>
+    <t>0.0254,0.0009,0.9857,0.0002</t>
+  </si>
+  <si>
+    <t>0.2405,0.0017,0.9131,0.0006</t>
+  </si>
+  <si>
+    <t>0.0058,0.0047,0.9949,0.0004</t>
+  </si>
+  <si>
+    <t>0.0093,0.9870,0.0040,0.0002</t>
+  </si>
+  <si>
+    <t>0.0104,0.0008,0.9897,0.0009</t>
+  </si>
+  <si>
+    <t>0.0527,0.3176,0.0102,0.8511</t>
+  </si>
+  <si>
+    <t>0.0042,0.9816,0.0059,0.0213</t>
+  </si>
+  <si>
+    <t>0.0034,0.9823,0.0366,0.0036</t>
+  </si>
+  <si>
+    <t>0.0005,0.9964,0.0011,0.0021</t>
+  </si>
+  <si>
+    <t>0.0062,0.1562,0.9472,0.0050</t>
+  </si>
+  <si>
+    <t>0.0040,0.1817,0.9644,0.0017</t>
+  </si>
+  <si>
+    <t>0.0204,0.0045,0.9751,0.0007</t>
+  </si>
+  <si>
+    <t>0.0018,0.0007,0.9973,0.0005</t>
+  </si>
+  <si>
+    <t>0.0216,0.0053,0.9787,0.0017</t>
+  </si>
+  <si>
+    <t>0.0346,0.1067,0.8113,0.0008</t>
+  </si>
+  <si>
+    <t>0.9852,0.0105,0.0017,0.0006</t>
+  </si>
+  <si>
+    <t>0.9814,0.0058,0.0093,0.0016</t>
+  </si>
+  <si>
+    <t>0.9949,0.0013,0.0007,0.0009</t>
+  </si>
+  <si>
+    <t>0.0105,0.0071,0.9870,0.0057</t>
+  </si>
+  <si>
+    <t>0.9953,0.0006,0.0004,0.0014</t>
+  </si>
+  <si>
+    <t>0.9918,0.0037,0.0030,0.0003</t>
+  </si>
+  <si>
+    <t>0.9933,0.0060,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.0017,0.6907,0.9772,0.0004</t>
+  </si>
+  <si>
+    <t>0.0005,0.2345,0.9927,0.0008</t>
+  </si>
+  <si>
+    <t>0.0056,0.0087,0.9849,0.0070</t>
+  </si>
+  <si>
+    <t>0.0010,0.8845,0.9730,0.0008</t>
+  </si>
+  <si>
+    <t>0.0031,0.0013,0.9961,0.0006</t>
+  </si>
+  <si>
+    <t>0.0441,0.9564,0.0053,0.0005</t>
+  </si>
+  <si>
+    <t>0.0016,0.9982,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.8523,0.0077,0.2699,0.0022</t>
+  </si>
+  <si>
+    <t>0.6877,0.1161,0.2051,0.0433</t>
+  </si>
+  <si>
+    <t>0.0086,0.0029,0.9919,0.0005</t>
+  </si>
+  <si>
+    <t>0.0027,0.9111,0.8971,0.0012</t>
+  </si>
+  <si>
+    <t>0.0084,0.8480,0.2984,0.0010</t>
+  </si>
+  <si>
+    <t>0.0002,0.9945,0.5041,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.9645,0.8965,0.0005</t>
+  </si>
+  <si>
+    <t>0.0870,0.0022,0.0830,0.8292</t>
+  </si>
+  <si>
+    <t>0.0010,0.0072,0.0012,0.9984</t>
+  </si>
+  <si>
+    <t>0.0065,0.0025,0.0024,0.9945</t>
+  </si>
+  <si>
+    <t>0.0118,0.0224,0.0100,0.9861</t>
+  </si>
+  <si>
+    <t>0.0167,0.0023,0.0085,0.9865</t>
+  </si>
+  <si>
+    <t>0.0046,0.0035,0.0019,0.9958</t>
+  </si>
+  <si>
+    <t>0.0008,0.9890,0.1858,0.0000</t>
+  </si>
+  <si>
+    <t>0.0091,0.5904,0.9400,0.0030</t>
+  </si>
+  <si>
+    <t>0.0083,0.7859,0.8033,0.0033</t>
+  </si>
+  <si>
+    <t>0.0008,0.8409,0.9784,0.0005</t>
+  </si>
+  <si>
+    <t>0.0005,0.9702,0.8649,0.0001</t>
+  </si>
+  <si>
+    <t>0.0029,0.9625,0.1306,0.0002</t>
+  </si>
+  <si>
+    <t>0.9982,0.0006,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9934,0.0047,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9899,0.0071,0.0011,0.0005</t>
+  </si>
+  <si>
+    <t>0.9915,0.0035,0.0013,0.0009</t>
+  </si>
+  <si>
+    <t>0.9914,0.0059,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9918,0.0024,0.0021,0.0014</t>
+  </si>
+  <si>
+    <t>0.9923,0.0037,0.0009,0.0004</t>
+  </si>
+  <si>
+    <t>0.9752,0.0147,0.0101,0.0016</t>
+  </si>
+  <si>
+    <t>0.9984,0.0002,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9974,0.0006,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9857,0.0024,0.0060,0.0029</t>
+  </si>
+  <si>
+    <t>0.9969,0.0007,0.0012,0.0003</t>
+  </si>
+  <si>
+    <t>0.9968,0.0007,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9895,0.0056,0.0020,0.0007</t>
+  </si>
+  <si>
+    <t>0.9958,0.0008,0.0011,0.0004</t>
+  </si>
+  <si>
+    <t>0.0085,0.0042,0.9896,0.0012</t>
+  </si>
+  <si>
+    <t>0.0154,0.0027,0.9822,0.0005</t>
+  </si>
+  <si>
+    <t>0.9963,0.0003,0.0027,0.0000</t>
+  </si>
+  <si>
+    <t>0.0121,0.0015,0.9907,0.0003</t>
+  </si>
+  <si>
+    <t>0.0051,0.9911,0.0010,0.0007</t>
+  </si>
+  <si>
+    <t>0.0122,0.9875,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.0085,0.9842,0.0039,0.0037</t>
+  </si>
+  <si>
+    <t>0.0424,0.9440,0.0256,0.0035</t>
+  </si>
+  <si>
+    <t>0.0050,0.9918,0.0013,0.0004</t>
+  </si>
+  <si>
+    <t>0.0010,0.9978,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.6831,0.4298,0.0021,0.0025</t>
+  </si>
+  <si>
+    <t>0.2146,0.5671,0.1101,0.0605</t>
+  </si>
+  <si>
+    <t>0.1202,0.0407,0.8548,0.0034</t>
+  </si>
+  <si>
+    <t>0.8727,0.0191,0.1234,0.0018</t>
+  </si>
+  <si>
+    <t>0.8842,0.0190,0.1102,0.0016</t>
+  </si>
+  <si>
+    <t>0.0483,0.0624,0.0354,0.9242</t>
+  </si>
+  <si>
+    <t>0.0006,0.9971,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.0019,0.9956,0.0027,0.0004</t>
+  </si>
+  <si>
+    <t>0.0016,0.9874,0.0193,0.0166</t>
+  </si>
+  <si>
+    <t>0.0028,0.9755,0.4765,0.0009</t>
+  </si>
+  <si>
+    <t>0.0240,0.9830,0.0018,0.0002</t>
+  </si>
+  <si>
+    <t>0.7754,0.3128,0.0031,0.0011</t>
+  </si>
+  <si>
+    <t>0.9217,0.0890,0.0081,0.0012</t>
+  </si>
+  <si>
+    <t>0.9838,0.0042,0.0011,0.0025</t>
+  </si>
+  <si>
+    <t>0.9926,0.0008,0.0049,0.0006</t>
+  </si>
+  <si>
+    <t>0.9905,0.0014,0.0043,0.0015</t>
+  </si>
+  <si>
+    <t>0.9914,0.0017,0.0056,0.0006</t>
+  </si>
+  <si>
+    <t>0.9936,0.0002,0.0015,0.0019</t>
+  </si>
+  <si>
+    <t>0.9984,0.0003,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9932,0.0008,0.0051,0.0007</t>
+  </si>
+  <si>
+    <t>0.9929,0.0010,0.0056,0.0004</t>
+  </si>
+  <si>
+    <t>0.0036,0.5767,0.9731,0.0009</t>
+  </si>
+  <si>
+    <t>0.0052,0.7466,0.8411,0.0016</t>
+  </si>
+  <si>
+    <t>0.0071,0.0691,0.9694,0.0002</t>
+  </si>
+  <si>
+    <t>0.0928,0.1135,0.8541,0.0044</t>
+  </si>
+  <si>
+    <t>0.9897,0.0017,0.0048,0.0002</t>
+  </si>
+  <si>
+    <t>0.6203,0.0074,0.5284,0.0022</t>
+  </si>
+  <si>
+    <t>0.6569,0.0016,0.4171,0.0109</t>
+  </si>
+  <si>
+    <t>0.9126,0.0146,0.0530,0.0081</t>
+  </si>
+  <si>
+    <t>0.0993,0.0019,0.0056,0.9575</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.0034,0.9991</t>
+  </si>
+  <si>
+    <t>0.0020,0.0107,0.0086,0.9940</t>
+  </si>
+  <si>
+    <t>0.0069,0.0006,0.0051,0.9933</t>
+  </si>
+  <si>
+    <t>0.0015,0.9301,0.8060,0.0030</t>
+  </si>
+  <si>
+    <t>0.9929,0.0018,0.0010,0.0010</t>
+  </si>
+  <si>
+    <t>0.0747,0.9496,0.0010,0.0008</t>
+  </si>
+  <si>
+    <t>0.9928,0.0014,0.0022,0.0010</t>
+  </si>
+  <si>
+    <t>0.7970,0.2646,0.0124,0.0036</t>
+  </si>
+  <si>
+    <t>0.9930,0.0007,0.0018,0.0023</t>
+  </si>
+  <si>
+    <t>0.2858,0.0108,0.0090,0.8473</t>
+  </si>
+  <si>
+    <t>0.9868,0.0022,0.0050,0.0020</t>
+  </si>
+  <si>
+    <t>0.0003,0.0906,0.9944,0.0089</t>
+  </si>
+  <si>
+    <t>0.9569,0.0005,0.0024,0.0410</t>
+  </si>
+  <si>
+    <t>0.9564,0.0051,0.0119,0.0243</t>
+  </si>
+  <si>
+    <t>0.8764,0.1186,0.0127,0.0067</t>
+  </si>
+  <si>
+    <t>0.9826,0.0047,0.0028,0.0017</t>
+  </si>
+  <si>
+    <t>0.9482,0.0220,0.0208,0.0024</t>
+  </si>
+  <si>
+    <t>0.2415,0.1951,0.4678,0.0168</t>
+  </si>
+  <si>
+    <t>0.7575,0.2552,0.0136,0.0015</t>
+  </si>
+  <si>
+    <t>0.9828,0.0109,0.0035,0.0001</t>
+  </si>
+  <si>
+    <t>0.9795,0.0028,0.0100,0.0037</t>
+  </si>
+  <si>
+    <t>0.9862,0.0010,0.0003,0.0102</t>
+  </si>
+  <si>
+    <t>0.9751,0.0081,0.0093,0.0045</t>
+  </si>
+  <si>
+    <t>0.9940,0.0002,0.0011,0.0028</t>
+  </si>
+  <si>
+    <t>0.9954,0.0008,0.0016,0.0005</t>
+  </si>
+  <si>
+    <t>0.9906,0.0017,0.0042,0.0009</t>
+  </si>
+  <si>
+    <t>0.9849,0.0047,0.0074,0.0016</t>
+  </si>
+  <si>
+    <t>0.9955,0.0005,0.0019,0.0004</t>
+  </si>
+  <si>
+    <t>0.8847,0.1560,0.0040,0.0020</t>
+  </si>
+  <si>
+    <t>0.6578,0.5577,0.0018,0.0003</t>
+  </si>
+  <si>
+    <t>0.8534,0.2391,0.0027,0.0012</t>
+  </si>
+  <si>
+    <t>0.0384,0.1141,0.9531,0.0015</t>
+  </si>
+  <si>
+    <t>0.9906,0.0098,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9615,0.0419,0.0072,0.0014</t>
+  </si>
+  <si>
+    <t>0.9895,0.0071,0.0009,0.0005</t>
+  </si>
+  <si>
+    <t>0.9830,0.0143,0.0026,0.0006</t>
+  </si>
+  <si>
+    <t>0.0035,0.0248,0.9958,0.0005</t>
+  </si>
+  <si>
+    <t>0.6910,0.2311,0.0690,0.0021</t>
+  </si>
+  <si>
+    <t>0.0105,0.0019,0.9913,0.0002</t>
+  </si>
+  <si>
+    <t>0.0111,0.0020,0.9913,0.0007</t>
+  </si>
+  <si>
+    <t>0.0034,0.0017,0.9946,0.0008</t>
+  </si>
+  <si>
+    <t>0.0148,0.0016,0.9850,0.0013</t>
+  </si>
+  <si>
+    <t>0.0044,0.0025,0.9932,0.0011</t>
+  </si>
+  <si>
+    <t>0.0095,0.0012,0.9929,0.0003</t>
+  </si>
+  <si>
+    <t>0.0019,0.0018,0.9973,0.0004</t>
+  </si>
+  <si>
+    <t>0.5021,0.0049,0.7353,0.0005</t>
+  </si>
+  <si>
+    <t>0.0361,0.0026,0.9709,0.0023</t>
+  </si>
+  <si>
+    <t>0.4549,0.0308,0.4827,0.0482</t>
+  </si>
+  <si>
+    <t>0.1279,0.1291,0.7400,0.0063</t>
+  </si>
+  <si>
+    <t>0.6509,0.0340,0.3621,0.0057</t>
+  </si>
+  <si>
+    <t>0.6967,0.0375,0.2810,0.0016</t>
+  </si>
+  <si>
+    <t>0.1959,0.0020,0.8828,0.0024</t>
+  </si>
+  <si>
+    <t>0.1295,0.1091,0.7149,0.0162</t>
+  </si>
+  <si>
+    <t>0.1884,0.8810,0.0022,0.0016</t>
+  </si>
+  <si>
+    <t>0.1253,0.9293,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.7036,0.4756,0.0010,0.0005</t>
+  </si>
+  <si>
+    <t>0.9799,0.0252,0.0024,0.0002</t>
+  </si>
+  <si>
+    <t>0.9240,0.1395,0.0035,0.0002</t>
+  </si>
+  <si>
+    <t>0.6580,0.1328,0.1542,0.0026</t>
+  </si>
+  <si>
+    <t>0.9762,0.0003,0.0577,0.0001</t>
+  </si>
+  <si>
+    <t>0.8480,0.0406,0.0115,0.0379</t>
+  </si>
+  <si>
+    <t>0.9098,0.0132,0.0775,0.0052</t>
+  </si>
+  <si>
+    <t>0.9560,0.0017,0.0414,0.0022</t>
+  </si>
+  <si>
+    <t>0.0097,0.0061,0.9782,0.0088</t>
+  </si>
+  <si>
+    <t>0.0275,0.0778,0.9147,0.0069</t>
+  </si>
+  <si>
+    <t>0.4814,0.0309,0.6178,0.0060</t>
+  </si>
+  <si>
+    <t>0.1913,0.0286,0.8002,0.0057</t>
+  </si>
+  <si>
+    <t>0.0013,0.8282,0.9358,0.0002</t>
+  </si>
+  <si>
+    <t>0.9960,0.0005,0.0003,0.0012</t>
+  </si>
+  <si>
+    <t>0.9907,0.0051,0.0013,0.0009</t>
+  </si>
+  <si>
+    <t>0.9912,0.0040,0.0017,0.0007</t>
+  </si>
+  <si>
+    <t>0.9923,0.0047,0.0015,0.0003</t>
+  </si>
+  <si>
+    <t>0.9925,0.0037,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.9925,0.0064,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9854,0.0047,0.0025,0.0035</t>
+  </si>
+  <si>
+    <t>0.9894,0.0013,0.0019,0.0037</t>
+  </si>
+  <si>
+    <t>0.0268,0.0768,0.9571,0.0024</t>
+  </si>
+  <si>
+    <t>0.3042,0.0837,0.6694,0.0192</t>
+  </si>
+  <si>
+    <t>0.9177,0.0115,0.0882,0.0029</t>
+  </si>
+  <si>
+    <t>0.0162,0.0128,0.9770,0.0014</t>
+  </si>
+  <si>
+    <t>0.0013,0.0042,0.9877,0.0187</t>
+  </si>
+  <si>
+    <t>0.0081,0.0123,0.9786,0.0033</t>
+  </si>
+  <si>
+    <t>0.0018,0.0007,0.9973,0.0004</t>
+  </si>
+  <si>
+    <t>0.0111,0.0057,0.9783,0.0038</t>
+  </si>
+  <si>
+    <t>0.0004,0.0022,0.9972,0.0024</t>
+  </si>
+  <si>
+    <t>0.0199,0.0104,0.9681,0.0025</t>
+  </si>
+  <si>
+    <t>0.0402,0.0581,0.8710,0.0067</t>
+  </si>
+  <si>
+    <t>0.8702,0.0021,0.1648,0.0049</t>
+  </si>
+  <si>
+    <t>0.7003,0.0005,0.3898,0.0046</t>
+  </si>
+  <si>
+    <t>0.9851,0.0002,0.0256,0.0002</t>
+  </si>
+  <si>
+    <t>0.9945,0.0018,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9836,0.0110,0.0021,0.0015</t>
+  </si>
+  <si>
+    <t>0.9906,0.0052,0.0018,0.0008</t>
+  </si>
+  <si>
+    <t>0.9665,0.0239,0.0029,0.0051</t>
+  </si>
+  <si>
+    <t>0.9930,0.0024,0.0019,0.0006</t>
+  </si>
+  <si>
+    <t>0.9826,0.0219,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.9881,0.0033,0.0024,0.0017</t>
+  </si>
+  <si>
+    <t>0.9901,0.0034,0.0006,0.0017</t>
+  </si>
+  <si>
+    <t>0.0068,0.0039,0.9907,0.0003</t>
+  </si>
+  <si>
+    <t>0.0006,0.0037,0.9968,0.0022</t>
+  </si>
+  <si>
+    <t>0.0289,0.1654,0.9211,0.0088</t>
+  </si>
+  <si>
+    <t>0.1958,0.0095,0.8414,0.0036</t>
+  </si>
+  <si>
+    <t>0.0013,0.0002,0.9966,0.0016</t>
+  </si>
+  <si>
+    <t>0.1127,0.0091,0.8852,0.0186</t>
+  </si>
+  <si>
+    <t>0.0112,0.0037,0.9680,0.0142</t>
+  </si>
+  <si>
+    <t>0.0194,0.0101,0.9389,0.0255</t>
+  </si>
+  <si>
+    <t>0.9708,0.0003,0.0011,0.0327</t>
+  </si>
+  <si>
+    <t>0.0110,0.0419,0.0023,0.9871</t>
+  </si>
+  <si>
+    <t>0.1332,0.0002,0.0012,0.9559</t>
+  </si>
+  <si>
+    <t>0.0097,0.0003,0.0012,0.9955</t>
+  </si>
+  <si>
+    <t>0.0025,0.0002,0.0015,0.9975</t>
+  </si>
+  <si>
+    <t>0.7263,0.0304,0.0030,0.1949</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1964,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -2135,7 +2132,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2149,7 +2146,7 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
         <v>278</v>
@@ -2163,7 +2160,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2191,7 +2188,7 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
         <v>281</v>
@@ -2205,7 +2202,7 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
         <v>282</v>
@@ -2219,7 +2216,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2289,7 +2286,7 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
         <v>288</v>
@@ -2303,7 +2300,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2317,7 +2314,7 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
         <v>290</v>
@@ -2331,7 +2328,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2345,7 +2342,7 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D30" t="s">
         <v>292</v>
@@ -2401,7 +2398,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2429,7 +2426,7 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
         <v>298</v>
@@ -2457,7 +2454,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2471,7 +2468,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2485,7 +2482,7 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
         <v>302</v>
@@ -2499,7 +2496,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
         <v>303</v>
@@ -2513,7 +2510,7 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
         <v>304</v>
@@ -2541,7 +2538,7 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
         <v>306</v>
@@ -2555,7 +2552,7 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
         <v>307</v>
@@ -2569,7 +2566,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
         <v>308</v>
@@ -2583,7 +2580,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2653,7 +2650,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2667,7 +2664,7 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
         <v>315</v>
@@ -2695,7 +2692,7 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
         <v>317</v>
@@ -2751,7 +2748,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2835,7 +2832,7 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
         <v>327</v>
@@ -2947,7 +2944,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2961,7 +2958,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -2989,7 +2986,7 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
         <v>338</v>
@@ -3003,7 +3000,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3014,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3031,7 +3028,7 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
         <v>341</v>
@@ -3045,7 +3042,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3056,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3070,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3087,7 +3084,7 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D83" t="s">
         <v>345</v>
@@ -3101,7 +3098,7 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
         <v>346</v>
@@ -3115,7 +3112,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3129,7 +3126,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
         <v>348</v>
@@ -3143,7 +3140,7 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
         <v>349</v>
@@ -3157,7 +3154,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
         <v>350</v>
@@ -3384,7 +3381,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3395,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3409,10 +3406,10 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3423,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3437,10 +3434,10 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3451,10 +3448,10 @@
         <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3465,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3479,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3493,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3507,10 +3504,10 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3521,10 +3518,10 @@
         <v>262</v>
       </c>
       <c r="C114" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3535,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3549,10 +3546,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3563,10 +3560,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,7 +3577,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,7 +3591,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,10 +3602,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3619,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3633,10 +3630,10 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3647,10 +3644,10 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3661,10 +3658,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3675,10 +3672,10 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3689,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3703,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3717,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3731,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3745,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3759,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3773,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3787,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3801,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3815,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3829,10 +3826,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,10 +3840,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3857,10 +3854,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3885,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3899,10 +3896,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3913,7 @@
         <v>259</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3927,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3941,10 +3938,10 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3955,10 +3952,10 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3969,10 +3966,10 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3983,10 +3980,10 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4011,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4039,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4053,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4067,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4081,10 +4078,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4095,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4109,10 +4106,10 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4123,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4137,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4151,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4165,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4179,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4193,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4207,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4221,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4235,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4249,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4263,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4277,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4291,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4305,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4319,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4333,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4347,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4361,10 +4358,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,7 +4375,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4386,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4403,10 +4400,10 @@
         <v>259</v>
       </c>
       <c r="C177" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4417,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4431,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4445,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4459,10 +4456,10 @@
         <v>261</v>
       </c>
       <c r="C181" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4473,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4487,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4515,10 +4512,10 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4529,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4557,10 +4554,10 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4571,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4582,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4599,10 +4596,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,7 +4613,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4624,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,7 +4641,7 @@
         <v>259</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,7 +4655,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,10 +4666,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4680,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,10 +4694,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,10 +4708,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4725,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4739,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4753,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4767,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4781,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4795,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4809,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4823,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,10 +4848,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4865,10 +4862,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4879,10 +4876,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,10 +4890,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4907,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4921,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4935,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4949,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4963,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4977,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +4991,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5005,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5019,10 +5016,10 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5030,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5047,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5061,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5075,10 +5072,10 @@
         <v>261</v>
       </c>
       <c r="C225" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5103,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5117,10 +5114,10 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5131,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5145,10 +5142,10 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5159,10 +5156,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5173,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5187,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5201,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5215,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5229,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5243,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5257,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5271,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5285,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5299,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5313,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5327,10 +5324,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5341,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5355,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5369,10 +5366,10 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5383,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5397,10 +5394,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5411,10 +5408,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5425,10 +5422,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5439,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5453,10 +5450,10 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5467,10 +5464,10 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5481,10 +5478,10 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5495,10 +5492,10 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5509,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
   </sheetData>
